--- a/Bases_de_Dados/FootyStats/Belgium Pro League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Belgium Pro League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP212"/>
+  <dimension ref="A1:BP213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.08</v>
@@ -3966,7 +3966,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.79</v>
@@ -5928,7 +5928,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR25" t="n">
         <v>0.99</v>
@@ -8762,7 +8762,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR38" t="n">
         <v>1.18</v>
@@ -10942,7 +10942,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR48" t="n">
         <v>1.18</v>
@@ -12029,7 +12029,7 @@
         <v>1</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.46</v>
@@ -13337,7 +13337,7 @@
         <v>0.67</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.92</v>
@@ -14427,7 +14427,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.23</v>
@@ -17479,7 +17479,7 @@
         <v>1.5</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.38</v>
@@ -18136,7 +18136,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR81" t="n">
         <v>1.76</v>
@@ -20534,7 +20534,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR92" t="n">
         <v>1.26</v>
@@ -22493,7 +22493,7 @@
         <v>1.83</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.62</v>
@@ -23804,7 +23804,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR107" t="n">
         <v>1.59</v>
@@ -24455,7 +24455,7 @@
         <v>1.86</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.69</v>
@@ -28164,7 +28164,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR127" t="n">
         <v>1.95</v>
@@ -28379,7 +28379,7 @@
         <v>1.88</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.46</v>
@@ -30562,7 +30562,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR138" t="n">
         <v>1.54</v>
@@ -31213,7 +31213,7 @@
         <v>1.75</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.86</v>
@@ -34701,7 +34701,7 @@
         <v>0.78</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.23</v>
@@ -35140,7 +35140,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR159" t="n">
         <v>1.25</v>
@@ -37320,7 +37320,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR169" t="n">
         <v>1.68</v>
@@ -38843,7 +38843,7 @@
         <v>0.9</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.77</v>
@@ -41680,7 +41680,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR189" t="n">
         <v>1.65</v>
@@ -44075,7 +44075,7 @@
         <v>0.83</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.86</v>
@@ -44950,7 +44950,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR204" t="n">
         <v>1.99</v>
@@ -46770,6 +46770,224 @@
       </c>
       <c r="BP212" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>8210258</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>46081.69791666666</v>
+      </c>
+      <c r="F213" t="n">
+        <v>27</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" t="n">
+        <v>1</v>
+      </c>
+      <c r="K213" t="n">
+        <v>2</v>
+      </c>
+      <c r="L213" t="n">
+        <v>5</v>
+      </c>
+      <c r="M213" t="n">
+        <v>1</v>
+      </c>
+      <c r="N213" t="n">
+        <v>6</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>['29', '47', '52', '71', '90+4']</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R213" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S213" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T213" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U213" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V213" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W213" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X213" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU213" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY213" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA213" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB213" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC213" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE213" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF213" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH213" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI213" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ213" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK213" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM213" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN213" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO213" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BP213" t="n">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Belgium Pro League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Belgium Pro League_20252026.xlsx
@@ -46945,10 +46945,10 @@
         <v>9</v>
       </c>
       <c r="BB213" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC213" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD213" t="n">
         <v>1.37</v>

--- a/Bases_de_Dados/FootyStats/Belgium Pro League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Belgium Pro League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.79</v>
@@ -3094,7 +3094,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.92</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.15</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.86</v>
@@ -4402,7 +4402,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR18" t="n">
         <v>1.47</v>
@@ -4835,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.62</v>
@@ -5056,7 +5056,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR21" t="n">
         <v>1.53</v>
@@ -6364,7 +6364,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR27" t="n">
         <v>2.21</v>
@@ -6582,7 +6582,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR28" t="n">
         <v>1.12</v>
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.92</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.08</v>
@@ -8544,7 +8544,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR37" t="n">
         <v>1.28</v>
@@ -8977,7 +8977,7 @@
         <v>2</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.86</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ41" t="n">
         <v>0.92</v>
@@ -9631,10 +9631,10 @@
         <v>0.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR42" t="n">
         <v>1</v>
@@ -9852,7 +9852,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR43" t="n">
         <v>1.76</v>
@@ -10503,7 +10503,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.79</v>
@@ -11160,7 +11160,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR49" t="n">
         <v>1.04</v>
@@ -11378,7 +11378,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR50" t="n">
         <v>1.11</v>
@@ -11596,7 +11596,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR51" t="n">
         <v>1.06</v>
@@ -11811,7 +11811,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.23</v>
@@ -12465,7 +12465,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.23</v>
@@ -12686,7 +12686,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR56" t="n">
         <v>1.64</v>
@@ -13119,7 +13119,7 @@
         <v>1</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.79</v>
@@ -13555,10 +13555,10 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR60" t="n">
         <v>1.61</v>
@@ -13773,7 +13773,7 @@
         <v>1</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.38</v>
@@ -14430,7 +14430,7 @@
         <v>2</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR64" t="n">
         <v>1.97</v>
@@ -15302,7 +15302,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR68" t="n">
         <v>1.3</v>
@@ -15953,10 +15953,10 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR71" t="n">
         <v>1.32</v>
@@ -16171,7 +16171,7 @@
         <v>1.25</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.62</v>
@@ -17697,10 +17697,10 @@
         <v>0.25</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR79" t="n">
         <v>1.66</v>
@@ -17918,7 +17918,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR80" t="n">
         <v>2</v>
@@ -18133,7 +18133,7 @@
         <v>0.75</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81" t="n">
         <v>1</v>
@@ -18572,7 +18572,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR83" t="n">
         <v>1.39</v>
@@ -19005,7 +19005,7 @@
         <v>1.4</v>
       </c>
       <c r="AP85" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.46</v>
@@ -19662,7 +19662,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR88" t="n">
         <v>1.37</v>
@@ -20095,7 +20095,7 @@
         <v>1.6</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.15</v>
@@ -20313,10 +20313,10 @@
         <v>0.2</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR91" t="n">
         <v>1.78</v>
@@ -20970,7 +20970,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR94" t="n">
         <v>1.56</v>
@@ -21185,7 +21185,7 @@
         <v>1.4</v>
       </c>
       <c r="AP95" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.79</v>
@@ -21403,7 +21403,7 @@
         <v>0.8</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.86</v>
@@ -22060,7 +22060,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR99" t="n">
         <v>1.42</v>
@@ -22278,7 +22278,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR100" t="n">
         <v>1.84</v>
@@ -22711,7 +22711,7 @@
         <v>1.33</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.46</v>
@@ -22932,7 +22932,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR103" t="n">
         <v>1.43</v>
@@ -23801,7 +23801,7 @@
         <v>0.67</v>
       </c>
       <c r="AP107" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ107" t="n">
         <v>1</v>
@@ -24019,7 +24019,7 @@
         <v>0.83</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.08</v>
@@ -24458,7 +24458,7 @@
         <v>2</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR110" t="n">
         <v>2.02</v>
@@ -25112,7 +25112,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR113" t="n">
         <v>1.34</v>
@@ -25763,10 +25763,10 @@
         <v>1</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR116" t="n">
         <v>1.83</v>
@@ -26199,7 +26199,7 @@
         <v>1.57</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.62</v>
@@ -26420,7 +26420,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR119" t="n">
         <v>1.5</v>
@@ -27725,7 +27725,7 @@
         <v>0.71</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.86</v>
@@ -28161,7 +28161,7 @@
         <v>1</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ127" t="n">
         <v>1</v>
@@ -28382,7 +28382,7 @@
         <v>2</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR128" t="n">
         <v>1.96</v>
@@ -28818,7 +28818,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ130" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR130" t="n">
         <v>1.19</v>
@@ -29033,7 +29033,7 @@
         <v>1.13</v>
       </c>
       <c r="AP131" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.38</v>
@@ -29254,7 +29254,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR132" t="n">
         <v>2</v>
@@ -29472,7 +29472,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR133" t="n">
         <v>1.75</v>
@@ -29905,7 +29905,7 @@
         <v>1.57</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.15</v>
@@ -30777,7 +30777,7 @@
         <v>1.75</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.62</v>
@@ -31652,7 +31652,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR143" t="n">
         <v>1.18</v>
@@ -31867,10 +31867,10 @@
         <v>1.67</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR144" t="n">
         <v>1.35</v>
@@ -32085,7 +32085,7 @@
         <v>0.75</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ145" t="n">
         <v>1.08</v>
@@ -32303,7 +32303,7 @@
         <v>1.33</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.46</v>
@@ -32739,7 +32739,7 @@
         <v>0.78</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ148" t="n">
         <v>0.86</v>
@@ -33178,7 +33178,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR150" t="n">
         <v>1.97</v>
@@ -34047,10 +34047,10 @@
         <v>1.6</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR154" t="n">
         <v>2.04</v>
@@ -34265,10 +34265,10 @@
         <v>1.6</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR155" t="n">
         <v>1.69</v>
@@ -35358,7 +35358,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR160" t="n">
         <v>1.26</v>
@@ -36227,7 +36227,7 @@
         <v>1.11</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.54</v>
@@ -37099,7 +37099,7 @@
         <v>1.5</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.38</v>
@@ -37538,7 +37538,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR170" t="n">
         <v>1.4</v>
@@ -38192,7 +38192,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR173" t="n">
         <v>1.51</v>
@@ -38625,7 +38625,7 @@
         <v>1.3</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ175" t="n">
         <v>1.54</v>
@@ -38846,7 +38846,7 @@
         <v>2</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR176" t="n">
         <v>1.87</v>
@@ -39282,7 +39282,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR178" t="n">
         <v>1.28</v>
@@ -39497,7 +39497,7 @@
         <v>0.9</v>
       </c>
       <c r="AP179" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ179" t="n">
         <v>0.92</v>
@@ -40590,7 +40590,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR184" t="n">
         <v>1.94</v>
@@ -41023,7 +41023,7 @@
         <v>1.82</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.86</v>
@@ -41244,7 +41244,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ187" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR187" t="n">
         <v>1.48</v>
@@ -41459,7 +41459,7 @@
         <v>1.27</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.54</v>
@@ -41895,7 +41895,7 @@
         <v>1.09</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ190" t="n">
         <v>1.15</v>
@@ -42988,7 +42988,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR195" t="n">
         <v>1.54</v>
@@ -43203,10 +43203,10 @@
         <v>1.08</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR196" t="n">
         <v>1.54</v>
@@ -43424,7 +43424,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR197" t="n">
         <v>1.37</v>
@@ -43639,10 +43639,10 @@
         <v>1.58</v>
       </c>
       <c r="AP198" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR198" t="n">
         <v>1.55</v>
@@ -45383,7 +45383,7 @@
         <v>1.25</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ206" t="n">
         <v>1.38</v>
@@ -46037,7 +46037,7 @@
         <v>1.33</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ209" t="n">
         <v>1.23</v>
@@ -46988,6 +46988,878 @@
       </c>
       <c r="BP213" t="n">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8210169</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>46082.39583333334</v>
+      </c>
+      <c r="F214" t="n">
+        <v>27</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>1</v>
+      </c>
+      <c r="L214" t="n">
+        <v>3</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>3</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>['4', '48', '90+1']</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S214" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U214" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V214" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X214" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8210121</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>46082.5</v>
+      </c>
+      <c r="F215" t="n">
+        <v>27</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R215" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S215" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U215" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V215" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X215" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>8210122</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>46082.60416666666</v>
+      </c>
+      <c r="F216" t="n">
+        <v>27</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>1</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>1</v>
+      </c>
+      <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="n">
+        <v>2</v>
+      </c>
+      <c r="N216" t="n">
+        <v>3</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>['74', '90+10']</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>4</v>
+      </c>
+      <c r="R216" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S216" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U216" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V216" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X216" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB216" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN216" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO216" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>8210162</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>46082.63541666666</v>
+      </c>
+      <c r="F217" t="n">
+        <v>27</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S217" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U217" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V217" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X217" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM217" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN217" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO217" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP217" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Belgium Pro League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Belgium Pro League_20252026.xlsx
@@ -47369,13 +47369,13 @@
         <v>4</v>
       </c>
       <c r="AX215" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY215" t="n">
         <v>8</v>
       </c>
       <c r="AZ215" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA215" t="n">
         <v>5</v>
@@ -47587,13 +47587,13 @@
         <v>6</v>
       </c>
       <c r="AX216" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY216" t="n">
         <v>9</v>
       </c>
       <c r="AZ216" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA216" t="n">
         <v>2</v>
@@ -47802,13 +47802,13 @@
         <v>6</v>
       </c>
       <c r="AW217" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX217" t="n">
         <v>5</v>
       </c>
       <c r="AY217" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ217" t="n">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Belgium Pro League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Belgium Pro League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.38</v>
@@ -1786,7 +1786,7 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.23</v>
@@ -3530,7 +3530,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.23</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.46</v>
@@ -7454,7 +7454,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR32" t="n">
         <v>0.58</v>
@@ -7672,7 +7672,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR33" t="n">
         <v>1.29</v>
@@ -8541,7 +8541,7 @@
         <v>2</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.43</v>
@@ -9416,7 +9416,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR41" t="n">
         <v>1.65</v>
@@ -10067,7 +10067,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.38</v>
@@ -11375,7 +11375,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.79</v>
@@ -12250,7 +12250,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR54" t="n">
         <v>1.58</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.86</v>
@@ -13340,7 +13340,7 @@
         <v>2</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR59" t="n">
         <v>2.03</v>
@@ -14648,7 +14648,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR65" t="n">
         <v>2</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.15</v>
@@ -15084,7 +15084,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR67" t="n">
         <v>1.27</v>
@@ -15520,7 +15520,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR69" t="n">
         <v>2.23</v>
@@ -17043,7 +17043,7 @@
         <v>1.5</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.79</v>
@@ -18351,10 +18351,10 @@
         <v>0.8</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR82" t="n">
         <v>1.21</v>
@@ -18569,7 +18569,7 @@
         <v>1.4</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.79</v>
@@ -19880,7 +19880,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR89" t="n">
         <v>1.4</v>
@@ -22929,7 +22929,7 @@
         <v>1.17</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.14</v>
@@ -23150,7 +23150,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR104" t="n">
         <v>1.61</v>
@@ -23365,7 +23365,7 @@
         <v>1.2</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.54</v>
@@ -24022,7 +24022,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR108" t="n">
         <v>1.23</v>
@@ -26635,7 +26635,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.15</v>
@@ -26853,7 +26853,7 @@
         <v>1.33</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.86</v>
@@ -27292,7 +27292,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR123" t="n">
         <v>1.19</v>
@@ -27946,7 +27946,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR126" t="n">
         <v>1.85</v>
@@ -28815,7 +28815,7 @@
         <v>0.63</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ130" t="n">
         <v>0.79</v>
@@ -30341,7 +30341,7 @@
         <v>1.25</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ137" t="n">
         <v>0.79</v>
@@ -31434,7 +31434,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR142" t="n">
         <v>1.62</v>
@@ -32088,7 +32088,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR145" t="n">
         <v>2.01</v>
@@ -33829,7 +33829,7 @@
         <v>0.88</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.54</v>
@@ -35137,7 +35137,7 @@
         <v>1.11</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ159" t="n">
         <v>1</v>
@@ -35576,7 +35576,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR161" t="n">
         <v>1.62</v>
@@ -36884,7 +36884,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR167" t="n">
         <v>1.15</v>
@@ -37753,7 +37753,7 @@
         <v>1.7</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.86</v>
@@ -38189,7 +38189,7 @@
         <v>1.55</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.43</v>
@@ -39064,7 +39064,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR177" t="n">
         <v>1.3</v>
@@ -39279,7 +39279,7 @@
         <v>1.09</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.14</v>
@@ -39500,7 +39500,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR179" t="n">
         <v>1.64</v>
@@ -39718,7 +39718,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR180" t="n">
         <v>1.43</v>
@@ -40805,7 +40805,7 @@
         <v>1.55</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ185" t="n">
         <v>1.62</v>
@@ -42552,7 +42552,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR193" t="n">
         <v>1.33</v>
@@ -42985,7 +42985,7 @@
         <v>0.83</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.79</v>
@@ -43860,7 +43860,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR199" t="n">
         <v>1.53</v>
@@ -45168,7 +45168,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ205" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR205" t="n">
         <v>1.91</v>
@@ -45601,7 +45601,7 @@
         <v>1.5</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ207" t="n">
         <v>1.62</v>
@@ -47860,6 +47860,442 @@
       </c>
       <c r="BP217" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>8210177</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>46087.69791666666</v>
+      </c>
+      <c r="F218" t="n">
+        <v>28</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R218" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S218" t="n">
+        <v>4</v>
+      </c>
+      <c r="T218" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U218" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V218" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W218" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X218" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY218" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA218" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB218" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>8210107</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>46088.5</v>
+      </c>
+      <c r="F219" t="n">
+        <v>28</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1</v>
+      </c>
+      <c r="K219" t="n">
+        <v>1</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>1</v>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R219" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S219" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U219" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V219" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W219" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X219" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU219" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW219" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX219" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY219" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ219" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA219" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB219" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC219" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BE219" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF219" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI219" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ219" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK219" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM219" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN219" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO219" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP219" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Belgium Pro League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Belgium Pro League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.54</v>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ16" t="n">
         <v>1</v>
@@ -5274,7 +5274,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR22" t="n">
         <v>1.4</v>
@@ -5710,7 +5710,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR24" t="n">
         <v>1.37</v>
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR26" t="n">
         <v>0.93</v>
@@ -6797,7 +6797,7 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.38</v>
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.15</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ38" t="n">
         <v>1</v>
@@ -10285,7 +10285,7 @@
         <v>3</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.15</v>
@@ -11157,7 +11157,7 @@
         <v>1.67</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.43</v>
@@ -11814,7 +11814,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR52" t="n">
         <v>1.41</v>
@@ -12032,7 +12032,7 @@
         <v>2</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR53" t="n">
         <v>2.55</v>
@@ -12468,7 +12468,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR55" t="n">
         <v>1.47</v>
@@ -15517,7 +15517,7 @@
         <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.21</v>
@@ -15738,7 +15738,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR70" t="n">
         <v>1.61</v>
@@ -16389,7 +16389,7 @@
         <v>0.75</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.86</v>
@@ -16610,7 +16610,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR74" t="n">
         <v>1.63</v>
@@ -18787,10 +18787,10 @@
         <v>1.4</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR84" t="n">
         <v>2.2</v>
@@ -19008,7 +19008,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR85" t="n">
         <v>1.53</v>
@@ -19223,7 +19223,7 @@
         <v>1.6</v>
       </c>
       <c r="AP86" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.62</v>
@@ -21621,7 +21621,7 @@
         <v>1.6</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.86</v>
@@ -21842,7 +21842,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR98" t="n">
         <v>1.36</v>
@@ -22714,7 +22714,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR102" t="n">
         <v>1.88</v>
@@ -23583,7 +23583,7 @@
         <v>1.33</v>
       </c>
       <c r="AP106" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.79</v>
@@ -24894,7 +24894,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR112" t="n">
         <v>1.56</v>
@@ -25545,7 +25545,7 @@
         <v>1</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.54</v>
@@ -25984,7 +25984,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR117" t="n">
         <v>1.87</v>
@@ -27289,7 +27289,7 @@
         <v>0.71</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.21</v>
@@ -29251,7 +29251,7 @@
         <v>1</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.14</v>
@@ -29690,7 +29690,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR134" t="n">
         <v>1.24</v>
@@ -30126,7 +30126,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR136" t="n">
         <v>1.54</v>
@@ -31649,7 +31649,7 @@
         <v>1.44</v>
       </c>
       <c r="AP143" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.79</v>
@@ -32306,7 +32306,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR146" t="n">
         <v>1.34</v>
@@ -32521,7 +32521,7 @@
         <v>1.33</v>
       </c>
       <c r="AP147" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.38</v>
@@ -32957,7 +32957,7 @@
         <v>1.22</v>
       </c>
       <c r="AP149" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.79</v>
@@ -34704,7 +34704,7 @@
         <v>2</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR157" t="n">
         <v>1.89</v>
@@ -36012,7 +36012,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR163" t="n">
         <v>1.31</v>
@@ -36445,7 +36445,7 @@
         <v>1.7</v>
       </c>
       <c r="AP165" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.62</v>
@@ -36881,7 +36881,7 @@
         <v>1</v>
       </c>
       <c r="AP167" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.93</v>
@@ -38410,7 +38410,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR174" t="n">
         <v>1.54</v>
@@ -39936,7 +39936,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR181" t="n">
         <v>1.72</v>
@@ -40369,10 +40369,10 @@
         <v>1.18</v>
       </c>
       <c r="AP183" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR183" t="n">
         <v>1.14</v>
@@ -40587,7 +40587,7 @@
         <v>1.73</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.79</v>
@@ -42113,7 +42113,7 @@
         <v>0.91</v>
       </c>
       <c r="AP191" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ191" t="n">
         <v>0.86</v>
@@ -42770,7 +42770,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR194" t="n">
         <v>1.29</v>
@@ -44729,7 +44729,7 @@
         <v>1.92</v>
       </c>
       <c r="AP203" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.86</v>
@@ -45165,7 +45165,7 @@
         <v>1</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AQ205" t="n">
         <v>0.93</v>
@@ -46040,7 +46040,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR209" t="n">
         <v>1.79</v>
@@ -48235,13 +48235,13 @@
         <v>4</v>
       </c>
       <c r="AV219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW219" t="n">
         <v>17</v>
       </c>
       <c r="AX219" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY219" t="n">
         <v>21</v>
@@ -48253,10 +48253,10 @@
         <v>9</v>
       </c>
       <c r="BB219" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BC219" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD219" t="n">
         <v>1.79</v>
@@ -48296,6 +48296,442 @@
       </c>
       <c r="BP219" t="n">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>8210174</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>46088.59375</v>
+      </c>
+      <c r="F220" t="n">
+        <v>28</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>2</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" t="n">
+        <v>3</v>
+      </c>
+      <c r="L220" t="n">
+        <v>2</v>
+      </c>
+      <c r="M220" t="n">
+        <v>2</v>
+      </c>
+      <c r="N220" t="n">
+        <v>4</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>['21', '39']</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>['6', '78']</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R220" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S220" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U220" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V220" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W220" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X220" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>8210260</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>46088.69791666666</v>
+      </c>
+      <c r="F221" t="n">
+        <v>28</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>1</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" t="n">
+        <v>2</v>
+      </c>
+      <c r="M221" t="n">
+        <v>1</v>
+      </c>
+      <c r="N221" t="n">
+        <v>3</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>['15', '52']</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R221" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S221" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T221" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U221" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V221" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W221" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X221" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO221" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP221" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
